--- a/www/download/COUNTRY.PRT.EXI382.xlsx
+++ b/www/download/COUNTRY.PRT.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3705</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>5.371</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4.481</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>4.49</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>4.585</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>4.927</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.963</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5.059</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>5.166</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>5.227</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>5.185</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>5.189</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>5.184</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>5.225</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>5.237</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>5.196</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>5.052</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>4.974</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.835</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>4.633</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>4.61</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>4.596</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4.661</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>4.733</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>5.016</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>5.15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>5.232</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>5.293</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.053</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.233</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3.211</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3.281</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3.488</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3.583</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3.676</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>3.725</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>3.791</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>3.786</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3.781</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>3.864</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3.871</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3.87</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>3.772</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>3.762</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>3.717</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>3.541</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>3.516</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>3.506</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3.554</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>3.61</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>3.829</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>3.922</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>4.039</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>10443.975</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>9849.452</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>9659.319</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>9652.003</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>10258.29</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>10375.261</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10349.377</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>10578.772</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>10615.527</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>10328.799</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>10617.514</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>10517.311</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>10557.791</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>10503.638</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>10410.561</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>10133.911</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>9998.044</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>9680.563</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>9245.295</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>9173.806</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>9132.209</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>9246.132</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>9359.829</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>9886.645</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>10133.554</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10284.518</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>10393.441</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7985.88</t>
+          <t>14448508897.6361</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3749.342</t>
+          <t>14736196794.097</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3650.307</t>
+          <t>12721199863.0296</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3737.373</t>
+          <t>12966544412.059</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3980.436</t>
+          <t>14082814859.4939</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4372.957</t>
+          <t>14176330507.1873</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4506.281</t>
+          <t>13886127727.5291</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4562.734</t>
+          <t>13747728451.3924</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4650.451</t>
+          <t>13170078988.6833</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4527.357</t>
+          <t>13703158800.3612</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4784.524</t>
+          <t>13703127779.5713</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4780.259</t>
+          <t>13158160010.5654</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5067.009</t>
+          <t>12845931036.8144</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5045.598</t>
+          <t>13960315607.8573</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5075.359</t>
+          <t>12180859606.0085</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>5010.567</t>
+          <t>11920000787.2296</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>5231.546</t>
+          <t>12293089429.9075</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5327.315</t>
+          <t>11629257435.0131</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5019.011</t>
+          <t>12046800905.6614</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>7062.971</t>
+          <t>10238675151.2234</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>7020.989</t>
+          <t>9835943504.49207</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>7100.891</t>
+          <t>9979196870.53994</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>7189.168</t>
+          <t>10116109149.0222</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7597.191</t>
+          <t>11180395110.3098</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>7767.92</t>
+          <t>10857743304.3196</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>7913.817</t>
+          <t>11455624876.6454</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>8006.393</t>
+          <t>11274333424.4597</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6153083346.71474</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4493684709.17</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3982428995.26143</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4127160731.92118</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4709112245.34831</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>5103827330.65177</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5181973021.11103</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5041573848.53629</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>4909514784.49955</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5037937622.95861</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4920135963.88062</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5106063175.58602</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>4921340323.73292</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>5277325428.2076</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>4998347201.19533</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>4648297582.11871</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4660327334.72892</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4361473929.2841</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>4514884404.60642</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>3910622423.25341</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>3605978695.24174</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3805994811.72274</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>4035911392.87343</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>4042845426.74944</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>3988178798.48623</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>4328277518.52398</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4070730377.7732</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>13287249.5614817</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>12191061.4303064</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10165570.8595657</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>9907090.43453689</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>10774942.3481217</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10558545.357219</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10041337.7997388</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>9788998.23629321</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>9384118.59922632</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>13810398.9246758</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>8134818.46821435</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>8091917.19718034</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>37718309973.1579</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>7477486.93567099</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>7324500.52934837</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>6958552.77036201</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>6681025.56064037</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>6692546.55458014</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>6686153.82686696</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>5659769.69120866</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>5337572.64267709</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5211650.49786752</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>5067892.88120639</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5137584.74726347</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>4973141.96777206</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>4948094.35046241</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>5148040.93783187</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20926.8976093966</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>44011.4627078967</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>46504.7430175768</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>48068.1694878053</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>56458.4300235234</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>66809.2149248152</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>67047.0219908535</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>66345.1677096935</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>60521.578152019</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>57759.3941856796</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>62181.0000140295</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>65234.321116371</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>68071.4738476531</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>67453.2414634759</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>65116.7978609514</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>73163.7158287618</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>74922.2748356161</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>79396.9590376929</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>73804.2483432693</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>76303.5419380096</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>84950.6780923756</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>79288.682375854</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>84824.0803852954</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>87552.6538184287</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>94573.8072457474</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>92685.811918308</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>91247.8087433641</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>53858.299933092</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>111981.426775587</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>105288.588334946</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>110331.561646843</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>126397.415632591</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>152095.205693625</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>149591.803056609</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>143562.533800988</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>126337.690751241</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>128459.190429168</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>137713.3068102</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>141454.297845776</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>143076.851364108</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>156237.00514866</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>136610.156673714</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>154165.658234339</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>165517.976398679</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>172826.4546974</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>174883.15876229</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>153848.778206589</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>166956.752295189</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>154392.523381454</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>165470.114365072</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>177862.809096873</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>184037.345496838</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>184715.730952591</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>178480.140986414</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.297866404138737</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.165641952505183</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.0833968403843224</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.0944445242725201</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.154737497724342</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.143200442198436</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.130392809526125</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.0949782474522823</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.0527676961718887</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.101347150594487</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.0275626456009153</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.0638073138503426</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.0295993909548464</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.0439100130091528</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.0154074528448223</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.0779359349271171</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.122570502936441</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.221448319163879</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.111658804570911</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.806099027722944</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.94704121515675</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.865712222703001</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.78129979746689</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.879169371021364</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.947736067617623</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.82839859280188</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.966819771855156</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1518.13602076707</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1389.85670826726</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1240.24571636866</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1258.05057974807</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1349.9347108553</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1424.61545543821</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1409.52372459817</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1353.44264390246</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1295.04478620394</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1343.45003278889</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1299.73212623971</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1350.2745406815</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1273.50696711897</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1363.12163972826</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1291.62933515844</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1232.34910313639</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1238.88862342294</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1173.35393970693</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1275.1749434008</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1112.17154935589</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1028.39589165106</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1070.86579129979</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1118.09078817686</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1055.94236378603</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1016.91239205116</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1084.77478493929</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1007.92302630482</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>3401097866.21441</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>2676699999.24492</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>1746064057.10429</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>1769632012.03175</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>1570312687.61246</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>2082179204.07053</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1909814083.16706</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>2012761898.98625</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>2081806739.86994</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1827550079.88303</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>1536083845.8323</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2171321300.91974</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>2016659967.46676</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>1967331228.77354</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>1895387828.94841</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>1883131217.98116</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>2882864842.95225</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>3382050292.03835</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>3851191789.45339</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>2762315753.83174</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>2479009310.72053</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>2811506748.34728</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>2526053794.20193</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>2495025119.70767</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>2348486992.50707</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>2715172857.99529</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>2104642994.28968</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3001031870.01046</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2521466577.7098</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1612611512.95136</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1664687295.61926</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1504278976.13403</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1898557023.61708</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1565577283.85082</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1532146956.83366</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1508004055.00853</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1185670699.98482</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1020698630.30942</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1633369162.38638</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1382690511.6629</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>1427388085.54075</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1376112144.73971</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1363163303.70216</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2268305033.38544</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2698087383.84875</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>3071051414.01542</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2056347858.4199</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>1780072423.7747</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2001145250.75874</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>1847673554.69916</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>1815319979.38006</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1642551861.00283</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>1931654124.69477</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2894534222.45513</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>400065996.203945</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>155233421.535116</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>133452544.152929</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>104944716.412484</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>66033711.4784284</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>183622180.45345</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>344236799.316237</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>480614942.152593</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>573802684.861408</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>641879379.898207</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>515385215.522876</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>537952138.533365</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>633969455.803864</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>539943143.232786</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>519275684.208704</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>519967914.278995</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>614559809.566805</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>683962908.189596</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>780140375.437968</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>705967895.411844</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>698936886.945833</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>810361497.588543</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>678380239.502767</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>679705140.32761</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>705935131.504248</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>783518733.300516</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-789891228.165452</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>1970.33773826645</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1159.63812940744</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>1136.81314232332</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>1139.234591233</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>1141.04919160632</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>1220.60989225674</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>1225.73196605409</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>1224.89503355742</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>1226.70825639654</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>1207.29519999967</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>1263.90807026804</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>1264.11714928011</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>1311.20199772244</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>1303.26695079474</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>1311.53005323288</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>1328.39338264592</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>1390.73982507812</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>1433.19119743935</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>1417.55945319972</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>2008.69195395279</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>2002.32918654249</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>1997.92739570254</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>1991.65489452904</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>1984.2945475906</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>1980.67694360535</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>1983.40069028997</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>1982.4029366444</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>1944.38810170011</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>2197.9496563418</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>2151.24807910694</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>2105.12606324954</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>2082.01376063001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>2090.6905654296</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>2045.89748151706</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>2047.76848625638</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>2031.01899860292</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1991.93855707464</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>2046.07916441822</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2028.68487548999</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>2020.47517893401</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>2005.46787589536</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>2003.76498893275</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>2006.07945997372</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>2009.98029833943</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>2002.10187789625</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>1995.74635725807</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>1989.79235041838</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>1987.10724663283</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1983.85166317243</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>1977.73560894213</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>1971.03016652531</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>1967.67256216774</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>1965.81819369666</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>1963.73104604942</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>28217.3308988555</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>27324.8085772703</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>30209.7452727503</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>32493.8226293623</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>34027.8249932359</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>40033.1270204243</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>41453.2367034368</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>42865.9679433085</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>43799.5858488224</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>44916.0617208038</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>45109.4852781924</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>53774.9949148043</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>57657.0462876189</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>57794.1299393578</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>50354.0389133147</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>57677.639577049</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>66483.7841749432</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>72499.8639412892</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>76613.6713446453</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>78402.6789570082</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>84253.4977291904</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>86386.4587391672</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>96758.2470551834</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>102051.56501361</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>106832.888202491</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>111661.025452285</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>114091.117937168</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2386661124.69683</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2734098989.55445</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2192480597.31473</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2243589848.34246</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2480879013.46792</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2435091636.50252</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2461229489.58678</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2418097750.42392</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2320026934.37787</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2403896378.79292</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2375218959.73871</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2410117226.45007</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2427126717.30626</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2658337411.78297</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2150433453.01614</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2250954871.94105</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2675253598.59319</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2757109986.20359</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>3244720255.0079</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2696355331.4085</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2561122284.65018</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2598949295.55225</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2910128427.69371</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>3275828120.52716</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>3304597673.62197</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>3431674498.33007</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3458601907.0969</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>35747.5064597127</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>36310.8640193242</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>41003.5140334007</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>45751.7434874409</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>50213.7806624798</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>58537.0742728485</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>59583.2594950992</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>58012.1187081929</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>56008.0797198022</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>60561.3665747217</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>63302.7334371151</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>70792.5280865638</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>74981.3274600918</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>80084.0751019387</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>66133.961181722</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>75620.0692779164</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>76121.4187163579</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>73589.1433040459</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>74164.4688505448</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>78064.4396812627</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>82516.2563977846</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>83589.4702165337</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>94171.2283051623</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>100809.876074234</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>106195.021161579</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>112893.381519749</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>116282.816061885</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10443.975</t>
+          <t>10053801035.6723</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9849.452</t>
+          <t>7236208757.85876</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>9659.319</t>
+          <t>5959005588.56548</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>9652.003</t>
+          <t>6510991883.70953</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>10258.29</t>
+          <t>7020406418.64554</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>10375.261</t>
+          <t>7387983919.6452</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10349.377</t>
+          <t>7295035311.12919</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>10578.772</t>
+          <t>6965318837.0637</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>10615.527</t>
+          <t>6475784009.6902</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10328.799</t>
+          <t>7100636438.39695</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10617.514</t>
+          <t>6954134190.76989</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>10517.311</t>
+          <t>7113506210.89485</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>10557.791</t>
+          <t>6595157568.65536</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>10503.638</t>
+          <t>7680268224.84939</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>10410.561</t>
+          <t>6368490290.09496</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10133.911</t>
+          <t>6346423850.8808</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>9998.044</t>
+          <t>6669489548.06132</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>9680.563</t>
+          <t>6257925748.65981</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>9245.295</t>
+          <t>6815347187.41888</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>9173.806</t>
+          <t>5422714189.49165</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>9132.209</t>
+          <t>4872201364.62886</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>9246.132</t>
+          <t>5113817141.86959</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>9359.829</t>
+          <t>5186993443.42324</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>9886.645</t>
+          <t>5647442141.41451</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>10133.554</t>
+          <t>5594868195.8698</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10284.518</t>
+          <t>6266436823.74259</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>10393.441</t>
+          <t>5776793170.32317</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>7985.88</t>
+          <t>-7530.17556085713</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3749.342</t>
+          <t>-8986.05544205393</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3650.307</t>
+          <t>-10793.7687606503</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3737.373</t>
+          <t>-13257.9208580786</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3980.436</t>
+          <t>-16185.9556692439</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4372.957</t>
+          <t>-18503.9472524241</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4506.281</t>
+          <t>-18130.0227916625</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4562.734</t>
+          <t>-15146.1507648844</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4650.451</t>
+          <t>-12208.4938709798</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4527.357</t>
+          <t>-15645.3048539179</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>4784.524</t>
+          <t>-18193.2481589227</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>4780.259</t>
+          <t>-17017.5331717594</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5067.009</t>
+          <t>-17324.2811724729</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5045.598</t>
+          <t>-22289.9451625809</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5075.359</t>
+          <t>-15779.9222684072</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>5010.567</t>
+          <t>-17942.4297008675</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>5231.546</t>
+          <t>-9637.63454141473</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>5327.315</t>
+          <t>-1089.27936275679</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>5019.011</t>
+          <t>2449.20249410052</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>7062.971</t>
+          <t>338.239275745461</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>7020.989</t>
+          <t>1737.24133140579</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>7100.891</t>
+          <t>2796.98852263355</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>7189.168</t>
+          <t>2587.0187500211</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>7597.191</t>
+          <t>1241.6889393756</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>7767.92</t>
+          <t>637.867040912749</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>7913.817</t>
+          <t>-1232.35606746353</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>8006.393</t>
+          <t>-2191.69812471686</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13653.546</t>
+          <t>-7667139910.97552</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>14372.857</t>
+          <t>-4502109768.30431</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12556.371</t>
+          <t>-3766524991.25075</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>12720.725</t>
+          <t>-4267402035.36707</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13880.743</t>
+          <t>-4539527405.17762</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>13882.036</t>
+          <t>-4952892283.14268</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13611.376</t>
+          <t>-4833805821.54241</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>13521.414</t>
+          <t>-4547221086.63978</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>13018.249</t>
+          <t>-4155757075.31233</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>13456.874</t>
+          <t>-4696740059.60403</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>13451.984</t>
+          <t>-4578915231.03118</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>12903.768</t>
+          <t>-4703388984.44478</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>12698.342</t>
+          <t>-4168030851.34911</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>13618.466</t>
+          <t>-5021930813.06641</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>12045.473</t>
+          <t>-4218056837.07883</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>11736.105</t>
+          <t>-4095468978.93975</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>12028.921</t>
+          <t>-3994235949.46813</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>11410.674</t>
+          <t>-3500815762.45622</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>11613.93</t>
+          <t>-3570626932.41098</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>10064.334</t>
+          <t>-2726358858.08316</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>9724.689</t>
+          <t>-2311079079.97868</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>9877.599</t>
+          <t>-2514867846.31734</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>10010.15</t>
+          <t>-2276865015.72954</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11124.48</t>
+          <t>-2371614020.88734</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>10700.661</t>
+          <t>-2290270522.24783</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11247.805</t>
+          <t>-2834762325.41251</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>11093.2</t>
+          <t>-2318191263.22627</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>38227.169107832</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>42604.5008142561</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>46143.8551824119</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>48703.4058648933</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>53551.551483378</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>60607.9734625736</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>63155.3375329627</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>66307.0310309677</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>68266.3949872608</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>69601.4225326313</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>72131.4266962663</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>75676.7272706713</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>79531.6478909729</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>80896.0356330328</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>77377.6198923793</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>78940.0818886593</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>78327.4479591549</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>72920.7366900409</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>74334.0039286948</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>74720.0317870945</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>79046.9807966437</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>81850.2600531933</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>90162.6333940023</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>91402.499930826</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>93996.2949162466</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>95743.9415838152</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>97593.2282374877</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>5614.037</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>5791.689</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>5618.806</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>5649.137</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>6290.426</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>6227.083</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6223.76</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>6353.297</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>6309.075</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>6161.382</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>6187.305</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>6068.134</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>6111.691</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>6027.18</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>5806.146</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>5656.977</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>5564.509</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>5342.514</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>5083.995</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>5078.02</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>5004.71</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>5124.843</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>5185.768</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>5503.53</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>5579.618</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>5748.151</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>5763.993</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>60739.8988316999</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>65610.0607341796</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>69924.9281291462</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>74933.5924317908</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>82393.393485504</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>94264.5643936264</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>98871.22254304</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>102819.244328746</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>106862.455430322</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>110380.752214314</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>116425.249695028</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>122740.844766693</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>129836.507611985</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>135026.726478246</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>131660.706972771</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>134167.244631477</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>132502.170145566</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>125834.439566683</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>128064.859646055</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>128101.108894688</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>133572.880416795</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>138287.50877608</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>154680.154434521</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>154142.396674406</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>159635.46937515</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>162093.740523391</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>165336.539831869</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>4873.35</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>3945.86</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>3532.208</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>3636.159</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>4082.524</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>4402.576</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4435.165</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>4329.652</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>4237.536</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>4315.502</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>4225.057</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>4366.393</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>4244.182</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>4524.253</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>4280.651</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>3964.879</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>3997.891</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>3712.624</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>3794.717</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>3312.462</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>3085.772</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>3249.068</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>3453.351</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>3483.714</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>3382.353</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>3633.455</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>3457.944</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>63.87</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-4.98</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2.78</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>5.38</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>9.74</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>4.91</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>13.24</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>9.48</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>19.39</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>11.52</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>18.57</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>26.37</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>30.86</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>43.49</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>32.26</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>113.22</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>127.53</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>118.55</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>108.18</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>118.08</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>129.66</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>117.8</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>131.54</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>16.591</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>13.043</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>12.739</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>13.966</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>13.462</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12.91</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>12.556</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>12.063</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>18.126</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>10.317</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>10.391</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>51692.296</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>9.445</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>9.393</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>8.929</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>8.49</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>8.467</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>8.397</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>7.169</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>6.795</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>6.628</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>6.47</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>6.546</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>6.325</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>6.275</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>6.51</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>56172.6889668902</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>58888.988632677</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>62955.8136316932</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>67150.767195984</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>71686.3904099089</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>71697.5703745318</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>76805.6998126719</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>79695.2416249861</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>80436.6876618858</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>85272.6931539262</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>87610.1717720721</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>90989.4108562612</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>96967.741765873</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>96634.1194457239</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>95182.9620249055</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>98926.5604103173</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>95481.117938323</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>92402.6097598222</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>93213.6486708835</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>95593.0575142851</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>98872.2332558746</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>102403.58414895</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>95095.6387557136</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>110414.603178936</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>115610.605671401</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>116888.903651672</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>120032.270032751</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7985880157.56661</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3749342000.0004</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3650307000.00171</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3737372999.99866</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3980436000.00006</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4372956999.99797</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4506280999.99978</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>4562734000.00106</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4650450999.99968</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>4527356999.99899</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>4784523999.99986</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>4780259000.00173</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>5067008999.99694</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5045598000.00147</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5075358999.99979</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>5010567000.00059</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>5231545999.99509</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>5327315000.00114</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>5019011000.00062</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>7062971356.42953</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>7020989140.61283</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>7100891039.77533</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>7189168146.71975</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>7597191297.72135</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>7767919689.91955</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>7913816524.12526</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>8006392992.89574</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10443974928.2431</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>9849451999.99968</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>9659319000.00126</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>9652002999.99918</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10258290000.0012</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>10375260999.9998</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10349376999.9989</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>10578772000</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>10615526999.9978</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>10328798999.9999</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>10617514000.0006</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>10517311000.0023</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>10557790999.9984</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>10503638000.0006</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>10410561000.0003</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>10133911000.0009</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>9998043999.99715</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>9680563000.0021</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>9245295000.00036</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>9173806026.24451</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>9132209154.05445</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>9246131932.82745</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>9359829443.56343</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>9886644999.19202</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>10133554339.6512</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10284518143.405</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>10393441257.0838</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5614036586.4669</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5791688803.5313</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>5618805797.10527</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5649136522.37644</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>6290426218.76172</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6227083275.7721</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6223760206.72148</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>6353296543.22858</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>6309074988.17043</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>6161382055.22518</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>6187304686.74404</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>6068134008.66522</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>6111690677.31266</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>6027179916.22491</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5806146424.61431</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>5656976788.88921</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>5564508731.23222</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>5342513551.08315</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>5083994891.65147</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>5078020039.53497</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>5004709656.23218</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>5124842535.79732</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>5185768191.04565</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>5503529757.66318</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>5579618199.85154</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>5748150887.02953</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>5763992645.55895</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5371342.74742336</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4481200.00000036</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4490100.00000149</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4585000.00000001</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4927100.00000052</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4962599.99999948</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5058599.99999839</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>5165999.99999981</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>5226699.99999996</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>5185300.00000038</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>5189200.00000077</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5184299.99999979</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>5225399.99999832</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>5237499.99999931</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5195500.00000009</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>5051599.99999886</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4974199.99999859</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4835199.99999908</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>4632500.00000118</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>4610433.85975205</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>4595730.38623309</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>4660697.22069932</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>4732598.93852542</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>5015978.53097347</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>5150020.65612343</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>5231673.08980152</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>5292700.99283354</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4053051.41472485</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3233200.00000022</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3211000.00000134</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3280599.99999973</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3488400.0000005</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3582599.99999917</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3676399.9999988</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3724999.99999973</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3791000.00000033</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3750000.0000002</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3785500.00000016</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3781499.99999921</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3864399.99999873</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3871499.99999972</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3869799.99999939</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>3771899.99999883</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>3761699.99999907</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>3717099.99999954</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>3540600.0000012</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>3516204.33512998</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>3506411.02761743</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>3554128.67106635</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>3609645.50960509</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>3828661.07602125</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>3921850.91819159</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>3990024.08482992</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>4038731.40263205</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10443974928.2431</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>9849451999.99968</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>9659319000.00126</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>9652002999.99918</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>10258290000.0012</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>10375260999.9998</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10349376999.9989</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>10578772000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>10615526999.9978</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>10328798999.9999</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>10617514000.0006</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>10517311000.0023</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>10557790999.9984</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10503638000.0006</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>10410561000.0003</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>10133911000.0009</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>9998043999.99715</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>9680563000.0021</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>9245295000.00036</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>9173806026.24451</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>9132209154.05445</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>9246131932.82745</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>9359829443.56343</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>9886644999.19202</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>10133554339.6512</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10284518143.405</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>10393441257.0838</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7985880157.56661</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3749342000.0004</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3650307000.00171</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3737372999.99866</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3980436000.00006</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4372956999.99797</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4506280999.99978</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4562734000.00106</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4650450999.99968</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4527356999.99899</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4784523999.99986</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4780259000.00173</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5067008999.99694</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5045598000.00147</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5075358999.99979</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>5010567000.00059</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>5231545999.99509</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>5327315000.00114</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>5019011000.00062</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>7062971356.42953</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>7020989140.61283</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>7100891039.77533</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>7189168146.71975</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>7597191297.72135</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>7767919689.91955</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>7913816524.12526</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>8006392992.89574</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>227959.93585918</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>246968.85061581</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>264879.105265816</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>281723.832283131</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>304203.724930674</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>337644.656445048</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>353822.78587401</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>363587.571886971</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>368035.982380887</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>390323.017592486</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>405324.044752263</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>429033.477275703</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>445648.620154888</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>464287.53150997</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>436479.012938816</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>454261.76852432</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>453670.605407486</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>429664.078431968</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>431579.818355482</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>439210.513497118</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>455745.337245873</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>469313.29664355</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>496395.565362109</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>527138.318274491</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>541945.660163874</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>553735.515857442</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>553632.313063426</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>67591.6887730842</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>73482.7300540375</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>78472.2753867382</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>84375.8632096185</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>92166.2085286687</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>103859.709863596</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>109117.410943202</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>114751.973989951</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>119293.557400584</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>123010.16240398</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>129598.189365468</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>136667.939960441</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>143210.733880426</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>147829.328459163</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>144258.515553118</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>146993.168675774</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>145535.116982817</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>138257.627105656</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>140382.769244845</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>141261.705109636</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>147328.480737726</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>153007.920253096</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>173445.537930394</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>170779.407210664</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>176711.823122714</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>180110.684003173</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>181422.311436819</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
